--- a/store/Jun-2026/Mail Attachment/BTC_Report_03-Jun-2026.xlsx
+++ b/store/Jun-2026/Mail Attachment/BTC_Report_03-Jun-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1446,37 +1446,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910381</t>
+          <t>WTI-20260603-3910590</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>in-fmcabbookings</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>BSR &amp; CO LLP.-BLR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MR.CHIRAG PILKHWAL</t>
+          <t>PAVITHRA ASHOK</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-06-03 20:00:00</t>
+          <t>2026-06-03 18:30:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>8146662428</t>
+          <t>9902095278</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>cpilkhwal@linkedin.com</t>
+          <t>pavithraashok@bsraffiliates.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1486,17 +1486,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-06-03 08:36:14.657000</t>
+          <t>2026-06-03 12:31:25.130000</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1506,34 +1506,30 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>BT260603111340</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>P : 1713482 T : 99</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2704</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Airport - Transfer Rate : 1600.00 ] PkgID:[181432]</t>
-        </is>
-      </c>
+          <t>BT260603111340</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910519</t>
+          <t>WTI-20260603-3910576</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1543,27 +1539,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MR.AMAN PANDEY</t>
+          <t>ANURADHA RAY</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-04 02:00:00</t>
+          <t>2026-06-03 19:45:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8005867409</t>
+          <t>9819717303</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ampandey@linkedin.com</t>
+          <t>anray@linkedin.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1578,7 +1574,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-06-03 11:45:41.533000</t>
+          <t>2026-06-03 12:21:33.163000</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1588,7 +1584,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1598,55 +1594,59 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BLR-LBLR-2326-CXI8</t>
+          <t>236748</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BLR-LBLR-2326-CXI8</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>MUM-LNCR-2326-21UA</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1300.00 ] PkgID:[181464]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910460</t>
+          <t>WTI-20260603-3910381</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>transportmoveinsync.com</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MS.AMRITA GHASGHASE</t>
+          <t>MR.CHIRAG PILKHWAL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-06-04 03:00:00</t>
+          <t>2026-06-03 20:00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9930350785</t>
+          <t>8146662428</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>aghasghase@linkedin.com</t>
+          <t>cpilkhwal@linkedin.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Taniya Gusain</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-03 10:36:56.017000</t>
+          <t>2026-06-03 08:36:14.657000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1681,55 +1681,59 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>PUN-LMUM-2326-V3U3</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>PUN-LMUM-2326-V3U3</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1600.00 ] PkgID:[181432]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910514</t>
+          <t>WTI-20260603-3910568</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vidya T</t>
+          <t>Soumita Das</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
+          <t>Check Point Software Technologies Ltd</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>RAVEENDRA BHAT</t>
+          <t>KAPIL AHUJA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-06-04 04:00:00</t>
+          <t>2026-06-03 20:25:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7397495272</t>
+          <t>9873467707</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>vidyat@grundfos.com</t>
+          <t>soumitad@checkpoint.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1739,12 +1743,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-06-03 11:40:56.627000</t>
+          <t>2026-06-03 12:17:38.870000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1754,7 +1758,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1762,57 +1766,45 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>109944</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>96400009</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>109944</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910494</t>
+          <t>WTI-20260603-3910570</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chaitanya Kulkarni</t>
+          <t>Sudha KS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ziehl-Abegg India Pvt. Ltd.</t>
+          <t>Centum Electronics Limited</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ASHISH TIDKE//VISHAL JOSHI</t>
+          <t>MR.NIKHIL MALLAVARAPU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-06-04 06:45:00</t>
+          <t>2026-06-03 22:20:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>8484862934</t>
+          <t>9008011866</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaitanya.Kulkarni@ziehl-abegg.in</t>
+          <t>sudhaks@centumelectronics.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1822,12 +1814,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-03 11:23:58.390000</t>
+          <t>2026-06-03 12:18:01.460000</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1837,7 +1829,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1853,37 +1845,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910415</t>
+          <t>WTI-20260603-3910519</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zoya Khan</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Omya India Private Limited</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>JOHNNY ZHANG</t>
+          <t>MR.AMAN PANDEY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-06-04 07:30:00</t>
+          <t>2026-06-04 02:00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9324725230</t>
+          <t>8005867409</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>zoya.khan@omya.com</t>
+          <t>ampandey@linkedin.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1893,12 +1885,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-03 09:51:28.943000</t>
+          <t>2026-06-03 11:45:41.533000</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1908,27 +1900,27 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>BLR-LBLR-2326-CXI8</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>BLR-LBLR-2326-CXI8</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1936,37 +1928,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910372</t>
+          <t>WTI-20260603-3910460</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phonepe Limited</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MR.MOHIT TYAGI</t>
+          <t>MS.AMRITA GHASGHASE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-06-04 08:00:00</t>
+          <t>2026-06-04 03:00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9760098845</t>
+          <t>9930350785</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>mohit.tyagi@phonepe.com</t>
+          <t>aghasghase@linkedin.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1976,12 +1968,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-06-03 08:11:39.390000</t>
+          <t>2026-06-03 10:36:56.017000</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1991,27 +1983,27 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Outstation</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>125201</t>
+          <t>PUN-LMUM-2326-V3U3</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MMT000101582497</t>
+          <t>PUN-LMUM-2326-V3U3</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
@@ -2019,37 +2011,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910371</t>
+          <t>WTI-20260603-3910597</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zoya Khan</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Omya India Private Limited</t>
+          <t>Phonepe Limited</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MR.DARSHANG SHAH</t>
+          <t>NIMISH LADKAT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-06-04 08:00:00</t>
+          <t>2026-06-04 04:00:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>8657426744</t>
+          <t>9604748700</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>zoya.khan@omya.com</t>
+          <t>nimish.ladkat@phonepe.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2059,12 +2051,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-06-03 07:56:28.460000</t>
+          <t>2026-06-03 12:36:25.503000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2074,53 +2066,65 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Outstation</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>422806</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>MMT000101582512</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910437</t>
+          <t>WTI-20260603-3910514</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mr. Raju Puchakayala</t>
+          <t>Vidya T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>John Snow India Pvt Ltd</t>
+          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SAISMITA MAHAPATRA</t>
+          <t>RAVEENDRA BHAT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:30:00</t>
+          <t>2026-06-04 04:00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>9437295291</t>
+          <t>7397495272</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>saismitamahapatra0@gmail.com</t>
+          <t>vidyat@grundfos.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:08:34.490000</t>
+          <t>2026-06-03 11:40:56.627000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2145,7 +2149,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Bhuwneshwar</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2155,17 +2159,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109944</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96400009</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109944</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
@@ -2173,37 +2177,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910475</t>
+          <t>WTI-20260603-3910494</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Chaitanya Kulkarni</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>Ziehl-Abegg India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MS.VAAGISHA</t>
+          <t>ASHISH TIDKE//VISHAL JOSHI</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:45:00</t>
+          <t>2026-06-04 06:45:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9818235942</t>
+          <t>8484862934</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>vaav@linkedin.com</t>
+          <t>Chaitanya.Kulkarni@ziehl-abegg.in</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2213,12 +2217,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Taniya Gusain</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:55:52.983000</t>
+          <t>2026-06-03 11:23:58.390000</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2228,7 +2232,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2236,57 +2240,45 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>5131</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910535</t>
+          <t>WTI-20260603-3910569</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>transportmoveinsync.com</t>
+          <t>Soumita Das</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
+          <t>Check Point Software Technologies Ltd</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MR.GAUTAM SHARMA</t>
+          <t>KAPIL AHUJA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-04 08:45:00</t>
+          <t>2026-06-04 07:00:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>8800020988</t>
+          <t>9873467707</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>gautsharma@linkedin.com</t>
+          <t>soumitad@checkpoint.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2301,7 +2293,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-03 11:50:08.767000</t>
+          <t>2026-06-03 12:17:57.893000</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2311,7 +2303,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2319,57 +2311,45 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>GRN-LNCR-2326-R071</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2311</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>GRN-LNCR-2326-R071</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910369</t>
+          <t>WTI-20260603-3910415</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>transportmoveinsync.com</t>
+          <t>Zoya Khan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>Omya India Private Limited</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>MS.ASHIMA PALAHA</t>
+          <t>JOHNNY ZHANG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-04 09:00:00</t>
+          <t>2026-06-04 07:30:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6364527610</t>
+          <t>9324725230</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>apalahababbar@linkedin.com</t>
+          <t>zoya.khan@omya.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2379,12 +2359,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Taniya Gusain</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-06-03 07:39:43.717000</t>
+          <t>2026-06-03 09:51:28.943000</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2394,7 +2374,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Ahmedabad Hub1</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2404,17 +2384,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ABD-LBLR-2326-WC1M</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>ABD-LBLR-2326-WC1M</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -2422,37 +2402,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910522</t>
+          <t>WTI-20260603-3910599</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vidya T</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
+          <t>Phonepe Limited</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RAVEENDRA BHAT</t>
+          <t>NIMISH LADKAT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-04 09:00:00</t>
+          <t>2026-06-04 08:00:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7397495272</t>
+          <t>9604748700</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>raveendra@grundfos.com</t>
+          <t>nimish.ladkat@phonepe.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2462,12 +2442,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-06-03 11:47:35.673000</t>
+          <t>2026-06-03 12:40:35.900000</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2477,7 +2457,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Raipur</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2487,17 +2467,17 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>109944</t>
+          <t>422806</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>96400009</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>109944</t>
+          <t>MMT000101582512</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -2505,37 +2485,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910367</t>
+          <t>WTI-20260603-3910372</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Etravel Helpdesk</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tech Mahindra Limited</t>
+          <t>Phonepe Limited</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MR.MATURI RAJ KUMAR</t>
+          <t>MR.MOHIT TYAGI</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-04 10:00:00</t>
+          <t>2026-06-04 08:00:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6300611392</t>
+          <t>9760098845</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Etravel.Helpdesk@techmahindra.com</t>
+          <t>mohit.tyagi@phonepe.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2550,7 +2530,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-03 07:35:39.267000</t>
+          <t>2026-06-03 08:11:39.390000</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2560,27 +2540,27 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Hyderabad Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Outstation</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>866588</t>
+          <t>125201</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>PID: 34974 Project Name- FT_Apple_Dubai_FP</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>ENS-D-4004</t>
+          <t>MMT000101582497</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -2588,37 +2568,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910508</t>
+          <t>WTI-20260603-3910371</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SUDARSAN</t>
+          <t>Zoya Khan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sundaram Finance Limited</t>
+          <t>Omya India Private Limited</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MR R SRIDHARAN</t>
+          <t>MR.DARSHANG SHAH</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-04 13:00:00</t>
+          <t>2026-06-04 08:00:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9444057552</t>
+          <t>8657426744</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>sfl.traveldesk@gmail.com</t>
+          <t>zoya.khan@omya.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2633,7 +2613,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-06-03 11:36:06.543000</t>
+          <t>2026-06-03 07:56:28.460000</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2643,65 +2623,53 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Chennai Hub</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
+          <t>Outstation</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910385</t>
+          <t>WTI-20260603-3910588</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>transportmoveinsync.com</t>
+          <t>in-fmcabbookings</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>KPMG India Services LLP - BLR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SHUBHAM GUPTA</t>
+          <t>JITESH SALVI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-05 01:45:00</t>
+          <t>2026-06-04 08:25:00</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>8764066357</t>
+          <t>9819128419</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>shubhamgupta@linkedin.com</t>
+          <t>jiteshsalvi@kpmg.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2716,7 +2684,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-06-03 08:54:51.830000</t>
+          <t>2026-06-03 12:29:42.250000</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2736,17 +2704,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>BT260603114148</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>P : 1709365 T : 01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BLR-LBLR-2326-JQZ4</t>
+          <t>BT260603114148</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
@@ -2754,37 +2722,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910403</t>
+          <t>WTI-20260603-3910549</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rupali Patwardhan</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Symrise Private Limited</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MS. RUPALI M. PATIL</t>
+          <t>SAUMITRA PIMPALKHARE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-05 04:30:00</t>
+          <t>2026-06-04 08:30:00</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9930633437</t>
+          <t>9108240923</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rupali.Patil@symrise.com</t>
+          <t>spimpalkhare@linkedin.com</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2794,12 +2762,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-06-03 09:38:54.160000</t>
+          <t>2026-06-03 12:06:00.567000</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2809,7 +2777,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2817,45 +2785,57 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PUN-LNCR-2326-X54Y</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910368</t>
+          <t>WTI-20260603-3910437</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Etravel Helpdesk</t>
+          <t>Mr. Raju Puchakayala</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tech Mahindra Limited</t>
+          <t>John Snow India Pvt Ltd</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MR.MATURI RAJ KUMAR</t>
+          <t>SAISMITA MAHAPATRA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-06-05 10:00:00</t>
+          <t>2026-06-04 08:30:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6300611392</t>
+          <t>9437295291</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Etravel.Helpdesk@techmahindra.com</t>
+          <t>saismitamahapatra0@gmail.com</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2870,7 +2850,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-06-03 07:35:57.197000</t>
+          <t>2026-06-03 10:08:34.490000</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2880,7 +2860,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Hyderabad Hub</t>
+          <t>Bhuwneshwar</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2890,17 +2870,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>866588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>PID: 34974 Project Name- FT_Apple_Dubai_FP</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>ENS-D-4004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -2908,37 +2888,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910517</t>
+          <t>WTI-20260603-3910558</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vidya T</t>
+          <t>Mr.Basavanthappa Gonepnara</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
+          <t>Bangalore International Airport Limited - CRD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>RAVEENDRA BHAT</t>
+          <t>RACHANA SINGH</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-06-05 11:15:00</t>
+          <t>2026-06-04 08:30:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>7397495272</t>
+          <t>9538882095</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>vidyat@grundfos.com</t>
+          <t>rachana@BIALAIRPORT.COM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2948,12 +2928,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-06-03 11:43:19.470000</t>
+          <t>2026-06-03 12:12:05.213000</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2963,7 +2943,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2973,17 +2953,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>109944</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>96400009</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>109944</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -2991,37 +2971,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910404</t>
+          <t>WTI-20260603-3910535</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rupali Patwardhan</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Symrise Private Limited</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MS. RUPALI M. PATIL</t>
+          <t>MR.GAUTAM SHARMA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-06-05 18:20:00</t>
+          <t>2026-06-04 08:45:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9930633437</t>
+          <t>8800020988</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rupali.Patil@symrise.com</t>
+          <t>gautsharma@linkedin.com</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3036,7 +3016,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-06-03 09:40:50.093000</t>
+          <t>2026-06-03 11:50:08.767000</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3046,7 +3026,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Mumbai Hub</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3054,45 +3034,57 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>GRN-LNCR-2326-R071</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>GRN-LNCR-2326-R071</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910538</t>
+          <t>WTI-20260603-3910475</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jayanta Bhattacharjee</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vodafone Idea Limited</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MR SUNIRMAL TALUKDAR</t>
+          <t>MS.VAAGISHA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-06-06 15:00:00</t>
+          <t>2026-06-04 08:45:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9088021977</t>
+          <t>9818235942</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>koladmin.helpdesk@vodafoneidea.com</t>
+          <t>vaav@linkedin.com</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3107,7 +3099,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-06-03 11:55:51.090000</t>
+          <t>2026-06-03 10:55:52.983000</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3117,7 +3109,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Kolkata Hub</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3125,45 +3117,57 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>5131</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910392</t>
+          <t>WTI-20260603-3910369</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SELF</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd - CV</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MR. PRIYESH PANDEY</t>
+          <t>MS.ASHIMA PALAHA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-06-07 23:00:00</t>
+          <t>2026-06-04 09:00:00</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>9922946139</t>
+          <t>6364527610</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>PRIYESH.PANDEY@TATAMOTORS.COM</t>
+          <t>apalahababbar@linkedin.com</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3173,12 +3177,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-06-03 09:24:53.183000</t>
+          <t>2026-06-03 07:39:43.717000</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3188,27 +3192,27 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Pune Hub 2</t>
+          <t>Ahmedabad Hub1</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>528825</t>
+          <t>ABD-LBLR-2326-WC1M</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Level 4 / 0003400075</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>11009923//28180859</t>
+          <t>ABD-LBLR-2326-WC1M</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -3216,37 +3220,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910489</t>
+          <t>WTI-20260603-3910522</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>in-fmcabbookingskpmg.com</t>
+          <t>Vidya T</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ANISH DE</t>
+          <t>RAVEENDRA BHAT</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-06-08 09:00:00</t>
+          <t>2026-06-04 09:00:00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9810453776</t>
+          <t>7397495272</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>anishde@kpmg.com</t>
+          <t>raveendra@grundfos.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3261,7 +3265,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-06-03 11:15:56.340000</t>
+          <t>2026-06-03 11:47:35.673000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3271,7 +3275,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Raipur</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3281,17 +3285,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>BT260602222524</t>
+          <t>109944</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>P : 1716318 T : 03</t>
+          <t>96400009</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BT260602222524</t>
+          <t>109944</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
@@ -3299,37 +3303,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910390</t>
+          <t>WTI-20260603-3910367</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T N Rakesh Raj</t>
+          <t>Etravel Helpdesk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SGS India Private Limited</t>
+          <t>Tech Mahindra Limited</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MR. P PRABHU // SOMESWARA RAO</t>
+          <t>MR.MATURI RAJ KUMAR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-06-08 10:30:00</t>
+          <t>2026-06-04 10:00:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9952188803</t>
+          <t>6300611392</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rakesh.Raj@sgs.com</t>
+          <t>Etravel.Helpdesk@techmahindra.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3339,12 +3343,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Yudhveer Singh W04209</t>
+          <t>Naveen S</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-06-03 09:23:17.037000</t>
+          <t>2026-06-03 07:35:39.267000</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3359,22 +3363,22 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Outstation</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866588</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>PID: 34974 Project Name- FT_Apple_Dubai_FP</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>ENS-D-4004</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -3382,37 +3386,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910373</t>
+          <t>WTI-20260603-3910554</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Monika Tanwar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phonepe Limited</t>
+          <t>Business Sweden India Private Limited</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MR.MOHIT TYAGI</t>
+          <t>MS SOFIA HOGMAN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-06-09 08:00:00</t>
+          <t>2026-06-04 10:45:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9760098845</t>
+          <t>9810036120</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>mohit.tyagi@phonepe.com</t>
+          <t>Sofia.hogman@business-sweden.se</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3422,12 +3426,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-06-03 08:14:15.540000</t>
+          <t>2026-06-03 12:09:03.413000</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3437,65 +3441,53 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Outstation</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>125201</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>3801</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>MMT000101582497</t>
-        </is>
-      </c>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910486</t>
+          <t>WTI-20260603-3910508</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>in-fmcabbookingskpmg.com</t>
+          <t>SUDARSAN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+          <t>Sundaram Finance Limited</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ANISH DE</t>
+          <t>MR R SRIDHARAN</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-06-09 08:00:00</t>
+          <t>2026-06-04 13:00:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>9810453776</t>
+          <t>9444057552</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>anishde@kpmg.com</t>
+          <t>sfl.traveldesk@gmail.com</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3510,7 +3502,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-06-03 11:09:33.583000</t>
+          <t>2026-06-03 11:36:06.543000</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3520,7 +3512,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Chennai Hub</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3530,17 +3522,17 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>BT260602222841</t>
+          <t>684</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>P : 1716318 T : 03</t>
+          <t>684</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BT260602222841</t>
+          <t>684</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
@@ -3548,37 +3540,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910537</t>
+          <t>WTI-20260603-3910598</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>in-fmcabbookingskpmg.com</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KPMG Global Services Management Private Limited - BLR</t>
+          <t>Phonepe Limited</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NAGARJUN P</t>
+          <t>NIMISH LADKAT</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-06-13 12:45:00</t>
+          <t>2026-06-04 22:00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9880912926</t>
+          <t>9604748700</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>nagarjunp@kpmg.com</t>
+          <t>nimish.ladkat@phonepe.com</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3588,12 +3580,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Naveen S</t>
+          <t>Taniya Gusain</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-06-03 11:55:27.873000</t>
+          <t>2026-06-03 12:38:05.900000</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3608,22 +3600,22 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>BT260603186277</t>
+          <t>422806</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>||P : 1197142 T : 01</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BT260603186277</t>
+          <t>MMT000101582512</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
@@ -3631,37 +3623,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910375</t>
+          <t>WTI-20260603-3910385</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yogender Singh</t>
+          <t>transportmoveinsync.com</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Markit India Services Private Limited</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>MR. GAURAV VANGAAL</t>
+          <t>SHUBHAM GUPTA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-06-15 06:15:00</t>
+          <t>2026-06-05 01:45:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>9810466002</t>
+          <t>8764066357</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>yogendersingh1@spglobal.com</t>
+          <t>shubhamgupta@linkedin.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3676,7 +3668,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-06-03 08:18:41.290000</t>
+          <t>2026-06-03 08:54:51.830000</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3686,53 +3678,65 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Local</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>BLR-LBLR-2326-JQZ4</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910377</t>
+          <t>WTI-20260603-3910403</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yogender Singh</t>
+          <t>Rupali Patwardhan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Markit India Services Private Limited</t>
+          <t>Symrise Private Limited</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MR. GAURAV VANGAAL</t>
+          <t>MS. RUPALI M. PATIL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-06-18 21:30:00</t>
+          <t>2026-06-05 04:30:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>9810466002</t>
+          <t>9930633437</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>yogendersingh1@spglobal.com</t>
+          <t>Rupali.Patil@symrise.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3747,7 +3751,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-06-03 08:21:07.550000</t>
+          <t>2026-06-03 09:38:54.160000</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3757,7 +3761,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3770,6 +3774,1677 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910571</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Soumita Das</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Check Point Software Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>KAPIL AHUJA</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-06-05 07:00:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9873467707</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>soumitad@checkpoint.com</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Taniya Gusain</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:18:08.190000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Chennai Hub</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910368</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Etravel Helpdesk</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Limited</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MR.MATURI RAJ KUMAR</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-06-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6300611392</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Etravel.Helpdesk@techmahindra.com</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-06-03 07:35:57.197000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>866588</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PID: 34974 Project Name- FT_Apple_Dubai_FP</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ENS-D-4004</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910517</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vidya T</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GRUNDFOS PUMPS INDIA PRIVATE LTD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>RAVEENDRA BHAT</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:15:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>7397495272</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>vidyat@grundfos.com</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:43:19.470000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>109944</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>96400009</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>109944</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910594</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>in-fmcabbookings</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>KPMG India Services LLP - BLR</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>JITESH SALVI</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-06-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9819128419</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>jiteshsalvi@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:34:56.813000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>BT260603114518</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>P : 1709365 T : 01</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>BT260603114518</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910404</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rupali Patwardhan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Symrise Private Limited</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MS. RUPALI M. PATIL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-06-05 18:20:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>9930633437</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rupali.Patil@symrise.com</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Taniya Gusain</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:40:50.093000</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910551</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KPMG Global Services Management Private Limited - BLR</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SIDDESHWARA GURURAJ H N</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-06-05 23:00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>9964979695</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>shn2@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:06:34.323000</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>BT260603186275</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>||P : 1521718 T : 99</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>BT260603186275</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910572</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Soumita Das</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Check Point Software Technologies Ltd</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>KAPIL AHUJA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-06-06 07:00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>9873467707</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>soumitad@checkpoint.com</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Taniya Gusain</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:18:21.590000</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Chennai Hub</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910538</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Jayanta Bhattacharjee</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Limited</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MR SUNIRMAL TALUKDAR</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-06-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>9088021977</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>koladmin.helpdesk@vodafoneidea.com</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Taniya Gusain</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:55:51.090000</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Kolkata Hub</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910542</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>KPMG Global Delivery Centre Private limited - BLR</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RAHUL CHORARIA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-06-07 10:00:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>9903875114</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>rahulchoraria@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:01:08.810000</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>BT260602186250</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>||P : 1634700 T : 01</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>BT260602186250</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910392</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SELF</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Tata Motors Ltd - CV</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MR. PRIYESH PANDEY</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-06-07 23:00:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>9922946139</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>PRIYESH.PANDEY@TATAMOTORS.COM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:24:53.183000</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Pune Hub 2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>528825</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Level 4 / 0003400075</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>11009923//28180859</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910489</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ANISH DE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-06-08 09:00:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>9810453776</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>anishde@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:15:56.340000</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>BT260602222524</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>P : 1716318 T : 03</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>BT260602222524</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910390</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>T N Rakesh Raj</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SGS India Private Limited</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MR. P PRABHU // SOMESWARA RAO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-06-08 10:30:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9952188803</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Rakesh.Raj@sgs.com</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:23:17.037000</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Outstation</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910560</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>KPMG Global Delivery Centre Private limited - BLR</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RAHUL CHORARIA</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-06-08 20:35:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9903875114</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>rahulchoraria@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:12:38.387000</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>BT260602186252</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>||P : 1634700 T : 01</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>BT260602186252</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910373</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Phonepe Limited</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MR.MOHIT TYAGI</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-06-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>9760098845</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>mohit.tyagi@phonepe.com</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:14:15.540000</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Outstation</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>125201</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>3801</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>MMT000101582497</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910486</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>KPMG Assurance and Consulting Services LLP - BLR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ANISH DE</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-06-09 08:00:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>9810453776</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>anishde@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:09:33.583000</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>BT260602222841</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>P : 1716318 T : 03</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>BT260602222841</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910561</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>KPMG Global Services Management Private Limited - BLR</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MR.NAGARJUN  P</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:45:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>9880912926</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>nagarjunp@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Taniya Gusain</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:13:08.513000</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>BT260603186276</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>||P : 1197142 T : 01</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>BT260603186276</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910537</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KPMG Global Services Management Private Limited - BLR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NAGARJUN P</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-06-13 12:45:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>9880912926</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>nagarjunp@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:55:27.873000</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>BT260603186277</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>||P : 1197142 T : 01</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>BT260603186277</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910375</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Yogender Singh</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Markit India Services Private Limited</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MR. GAURAV VANGAAL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-06-15 06:15:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>9810466002</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>yogendersingh1@spglobal.com</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:18:41.290000</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910567</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KPMG Global Services Management Private Limited - Haryana</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VISHAL PANDEY</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:20:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>9004666416</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>vishalpandey3@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:17:13.510000</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>BT260603186285</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>||P : 1724894 T : 07</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>BT260603186285</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910377</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Yogender Singh</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Markit India Services Private Limited</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MR. GAURAV VANGAAL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-06-18 21:30:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>9810466002</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>yogendersingh1@spglobal.com</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-06-03 08:21:07.550000</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910575</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>in-fmcabbookingskpmg.com</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KPMG Global Services Management Private Limited - Haryana</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VISHAL PANDEY</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-06-24 17:00:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>9004666416</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>vishalpandey3@kpmg.com</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:21:20.003000</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>BT260603186287</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>||P : 1724894 T : 07</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>BT260603186287</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
